--- a/excel/04_analisis.xlsx
+++ b/excel/04_analisis.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Fructosamina est." sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Laboratorio" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Bibliografia" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Notas IA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Leyenda" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Notas IA" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9108,6 +9109,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Abreviatura</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Significado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TIR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tiempo dentro del rango: % de lecturas en 100-250 mg/dL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TAR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tiempo por encima del rango: % de lecturas &gt; 250 mg/dL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TBR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tiempo por debajo del rango: % de lecturas &lt; 80 mg/dL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Coeficiente de variación: desviación estándar / media x 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Desviación estándar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Glucosa (lecturas de planillas, mg/dL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fructosamina (µmol/L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eAG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Glucosa promedio estimada (estimated average glucose)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CGM / BG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Monitorización continua de glucosa / Glucosa sanguínea</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UCCR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cociente cortisol-creatinina urinaria (control del Cushing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cociente proteína-creatinina urinaria (proteinuria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LPCE / cPLI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lipasa pancreática específica canina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hto / Hb</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hematocrito / Hemoglobina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T4 libre / TSH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tiroxina libre / Hormona estimulante de la tiroides</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALT (GPT) / FAL / GGT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Enzimas hepáticas: alanina-aminotransferasa / fosfatasa alcalina / gamma-glutamil transferasa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/excel/04_analisis.xlsx
+++ b/excel/04_analisis.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -56,12 +53,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,22 +420,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
@@ -474,17 +467,17 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>CV%</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>SD</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>CV%</t>
         </is>
       </c>
     </row>
@@ -496,10 +489,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>82.59999999999999</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -508,13 +501,13 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>226</v>
+        <v>24.86038028155109</v>
       </c>
       <c r="H2" t="n">
-        <v>56</v>
+        <v>225.7391304347826</v>
       </c>
       <c r="I2" t="n">
-        <v>24.9</v>
+        <v>56.11960627035358</v>
       </c>
     </row>
     <row r="3">
@@ -525,10 +518,10 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>61.01694915254237</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>38.98305084745763</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -537,13 +530,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>252</v>
+        <v>37.35064200709229</v>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>252.271186440678</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>94.22490773450197</v>
       </c>
     </row>
     <row r="4">
@@ -554,10 +547,10 @@
         <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>32.8</v>
+        <v>32.8125</v>
       </c>
       <c r="D4" t="n">
-        <v>67.2</v>
+        <v>67.1875</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -566,13 +559,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>299</v>
+        <v>35.96781389862563</v>
       </c>
       <c r="H4" t="n">
-        <v>107</v>
+        <v>298.5625</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>107.3864043710841</v>
       </c>
     </row>
     <row r="5">
@@ -595,13 +588,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>267</v>
+        <v>24.81471441817527</v>
       </c>
       <c r="H5" t="n">
-        <v>66</v>
+        <v>267.25</v>
       </c>
       <c r="I5" t="n">
-        <v>24.8</v>
+        <v>66.31732428257341</v>
       </c>
     </row>
     <row r="6">
@@ -612,25 +605,25 @@
         <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>51.6</v>
+        <v>51.5625</v>
       </c>
       <c r="D6" t="n">
-        <v>39.1</v>
+        <v>39.0625</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7</v>
+        <v>4.6875</v>
       </c>
       <c r="G6" t="n">
-        <v>226</v>
+        <v>43.21897373298318</v>
       </c>
       <c r="H6" t="n">
-        <v>98</v>
+        <v>225.8125</v>
       </c>
       <c r="I6" t="n">
-        <v>43.2</v>
+        <v>97.59384506079265</v>
       </c>
     </row>
     <row r="7">
@@ -641,25 +634,25 @@
         <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>63.5</v>
+        <v>63.49206349206349</v>
       </c>
       <c r="D7" t="n">
-        <v>23.8</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="E7" t="n">
-        <v>7.9</v>
+        <v>7.936507936507936</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3</v>
+        <v>6.349206349206349</v>
       </c>
       <c r="G7" t="n">
-        <v>193</v>
+        <v>37.37801591386275</v>
       </c>
       <c r="H7" t="n">
-        <v>72</v>
+        <v>193.1269841269841</v>
       </c>
       <c r="I7" t="n">
-        <v>37.4</v>
+        <v>72.18703486094731</v>
       </c>
     </row>
     <row r="8">
@@ -667,13 +660,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>46.2</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -682,122 +675,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>27.56440020821544</v>
       </c>
       <c r="H8" t="n">
-        <v>72</v>
+        <v>250.1052631578947</v>
       </c>
       <c r="I8" t="n">
-        <v>28.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>359</v>
-      </c>
-      <c r="C9" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>46</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>246</v>
-      </c>
-      <c r="H9" t="n">
-        <v>93</v>
-      </c>
-      <c r="I9" t="n">
-        <v>37.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mediodia</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>173</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>223</v>
-      </c>
-      <c r="H10" t="n">
-        <v>91</v>
-      </c>
-      <c r="I10" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>medianoche</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>176</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>271</v>
-      </c>
-      <c r="H11" t="n">
-        <v>88</v>
-      </c>
-      <c r="I11" t="n">
-        <v>32.4</v>
+        <v>68.9400156786525</v>
       </c>
     </row>
   </sheetData>
@@ -811,15 +695,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Parametro</t>
         </is>
@@ -837,7 +721,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +731,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>51.35028248587571</v>
       </c>
     </row>
     <row r="4">
@@ -857,115 +741,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.59999999999999</v>
+        <v>94.79863531181421</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank p</t>
+          <t>Wilcoxon p</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.608509208902595e-10</v>
+        <v>9.587512603785135e-11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>% días con noche &gt; día</t>
+          <t>% días noche &gt; mediodía</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Binom p (noc&gt;día)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.207079639264293e-07</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gap por mes</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 4</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 5</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>51.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 6</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>35.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 7</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>78.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 8</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>59.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mes 9</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>71.90000000000001</v>
+        <v>70.62146892655367</v>
       </c>
     </row>
   </sheetData>
@@ -979,19 +775,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
@@ -1037,14 +833,14 @@
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>205</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>mediodia</t>
+          <t>medianoche</t>
         </is>
       </c>
     </row>
@@ -1253,18 +1049,6 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>medianoche</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Interpretación</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Overshoot moderado (255-295 en 5/9), NO Somogyi clásico (necesita máx 400-800 y dosis &gt;=2,2 UI/kg). La curva 8-10/8 rebotó a 341 tras rescate con miel.</t>
         </is>
       </c>
     </row>
@@ -1279,15 +1063,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Parametro</t>
         </is>
@@ -1317,7 +1101,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>246</v>
+        <v>246.2048517520216</v>
       </c>
     </row>
     <row r="4">
@@ -1327,51 +1111,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>433</v>
+        <v>433.5675453424095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Media últimas 3 sem (24/8-13/9)</t>
+          <t>Media últimas 4 sem (24/8-19/9)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230</v>
+        <v>234.3518518518518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F estimada últimas 3 sem (µmol/L)</t>
+          <t>F estimada últimas 4 sem (µmol/L)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Clasificación canina</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>&lt;360 BUENO · 360-442 REGULAR · &gt;=443 MALO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Advertencia (Kuzi 2023)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Fructosamina baja puede reflejar hipoglucemias recientes (496 vs 572 µmol/L), no buen control. Leer siempre con la planilla.</t>
-        </is>
+        <v>413.4777150031387</v>
       </c>
     </row>
   </sheetData>
@@ -1388,17 +1148,17 @@
   <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
@@ -1430,7 +1190,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>origen</t>
+          <t>notas</t>
         </is>
       </c>
     </row>
@@ -1449,11 +1209,9 @@
         <v>361</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>LAB06</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1470,11 +1228,9 @@
         <v>1.35</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>LAB06</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1491,11 +1247,9 @@
         <v>69</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LAB06</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1512,11 +1266,9 @@
         <v>1020</v>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LAB06</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1533,11 +1285,9 @@
         <v>1020</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LAB06</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1550,12 +1300,15 @@
           <t>PH_ORINA</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACIDO</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LAB06</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1572,11 +1325,9 @@
         <v>316</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1593,11 +1344,9 @@
         <v>1652</v>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1614,11 +1363,9 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1635,11 +1382,9 @@
         <v>11.7</v>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1656,11 +1401,9 @@
         <v>240</v>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1677,11 +1420,9 @@
         <v>0.7</v>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1698,11 +1439,9 @@
         <v>3</v>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1719,11 +1458,9 @@
         <v>5461000</v>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1740,11 +1477,9 @@
         <v>97</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1761,11 +1496,9 @@
         <v>9</v>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1782,11 +1515,9 @@
         <v>130</v>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1803,11 +1534,9 @@
         <v>36</v>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,11 +1553,9 @@
         <v>13</v>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1845,11 +1572,9 @@
         <v>12760</v>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1866,11 +1591,9 @@
         <v>30</v>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1887,11 +1610,9 @@
         <v>4</v>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1908,11 +1629,9 @@
         <v>59</v>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1929,11 +1648,9 @@
         <v>56000</v>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1950,11 +1667,9 @@
         <v>5.4</v>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1971,11 +1686,9 @@
         <v>7.6</v>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1992,11 +1705,9 @@
         <v>26.1</v>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2013,11 +1724,9 @@
         <v>141</v>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2034,11 +1743,9 @@
         <v>34.2</v>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>LAB07</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2059,11 +1766,9 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>LAB08</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2084,17 +1789,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8500000</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2115,11 +1820,9 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2140,17 +1843,17 @@
           <t>pg</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>13</v>
-      </c>
-      <c r="F34" t="n">
-        <v>17</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2171,17 +1874,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>35</v>
-      </c>
-      <c r="F35" t="n">
-        <v>45</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2202,17 +1905,17 @@
           <t>gr/dl</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>8</v>
-      </c>
-      <c r="F36" t="n">
-        <v>15</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2233,14 +1936,13 @@
           <t>seg</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>21</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2261,17 +1963,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F38" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2292,17 +1994,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>12</v>
-      </c>
-      <c r="F39" t="n">
-        <v>35</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2323,17 +2025,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>30</v>
-      </c>
-      <c r="F40" t="n">
-        <v>35</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2354,17 +2056,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" t="n">
-        <v>10</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2385,17 +2087,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2416,17 +2118,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F43" t="n">
-        <v>77</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2447,17 +2149,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F44" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>600000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2474,11 +2176,9 @@
         <v>18</v>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2499,14 +2199,13 @@
           <t>seg</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2527,17 +2226,17 @@
           <t>fl</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>40</v>
-      </c>
-      <c r="F47" t="n">
-        <v>70</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>LAB12</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2550,12 +2249,15 @@
           <t>BACTERIURIA</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2568,12 +2270,15 @@
           <t>CELULAS_SEDIMENTO</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Escasas planas aisladas</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2586,12 +2291,15 @@
           <t>CILINDROS</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2604,12 +2312,15 @@
           <t>CRISTALES_ORINA</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Uratos de sodio amorfos</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2622,12 +2333,15 @@
           <t>HB_MIOGLOBULINA_ORINA</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2640,12 +2354,15 @@
           <t>HEMATIES_SEDIMENTO</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2658,12 +2375,15 @@
           <t>LEUCOCITOS_SEDIMENTO</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Escasos 1 a 3 por campo</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>LAB09</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2676,12 +2396,15 @@
           <t>ASPECTO_ORINA</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Limpido</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2694,12 +2417,15 @@
           <t>BILIRRUBINA_ORINA</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2712,12 +2438,15 @@
           <t>CETONAS_ORINA</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2730,12 +2459,15 @@
           <t>COLOR_ORINA</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ambar claro</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2752,11 +2484,9 @@
         <v>4620</v>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2773,11 +2503,9 @@
         <v>40.39</v>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2794,11 +2522,9 @@
         <v>1010</v>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2815,11 +2541,9 @@
         <v>357</v>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2836,11 +2560,9 @@
         <v>5</v>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2853,12 +2575,15 @@
           <t>PROTEINAS_ORINA</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>LAB10</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2879,17 +2604,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>4</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2910,17 +2635,17 @@
           <t>U/l</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>12</v>
-      </c>
-      <c r="F66" t="n">
-        <v>94</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2941,17 +2666,17 @@
           <t>U/l</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>9</v>
-      </c>
-      <c r="F67" t="n">
-        <v>56</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2972,17 +2697,17 @@
           <t>mmol/l</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>108</v>
-      </c>
-      <c r="F68" t="n">
-        <v>128</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3003,17 +2728,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>100</v>
-      </c>
-      <c r="F69" t="n">
-        <v>299</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3034,17 +2759,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3065,17 +2790,17 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>90</v>
-      </c>
-      <c r="F71" t="n">
-        <v>250</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3096,14 +2821,13 @@
           <t>U/l</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>10</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3124,17 +2848,17 @@
           <t>mmol/l</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F73" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3155,17 +2879,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F74" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3186,17 +2910,17 @@
           <t>mmol/l</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>146</v>
-      </c>
-      <c r="F75" t="n">
-        <v>159</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3217,17 +2941,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>17</v>
-      </c>
-      <c r="F76" t="n">
-        <v>200</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3248,17 +2972,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>10</v>
-      </c>
-      <c r="F77" t="n">
-        <v>60</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>LAB13</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3279,17 +3003,17 @@
           <t>ug/dl</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>6</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>LAB11</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3310,17 +3034,17 @@
           <t>ng/dl</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>LAB11</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3341,17 +3065,17 @@
           <t>ug/dl</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>LAB11</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3372,17 +3096,17 @@
           <t>ng/ml</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>LAB11</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3403,17 +3127,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3434,17 +3158,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F83" t="n">
-        <v>10</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3465,17 +3189,17 @@
           <t>10^12/L</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F84" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3496,17 +3220,17 @@
           <t>pg</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>20</v>
-      </c>
-      <c r="F85" t="n">
-        <v>27</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3527,17 +3251,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>33</v>
-      </c>
-      <c r="F86" t="n">
-        <v>56</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3558,17 +3282,17 @@
           <t>g/dL</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>11</v>
-      </c>
-      <c r="F87" t="n">
-        <v>19</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3589,17 +3313,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>6</v>
-      </c>
-      <c r="F88" t="n">
-        <v>17</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3620,17 +3344,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>4.91</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3651,17 +3375,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>12</v>
-      </c>
-      <c r="F90" t="n">
-        <v>33</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3682,17 +3406,17 @@
           <t>g/L</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>300</v>
-      </c>
-      <c r="F91" t="n">
-        <v>380</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3713,17 +3437,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3744,17 +3468,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" t="n">
-        <v>13</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3775,17 +3499,17 @@
           <t>fL</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>8</v>
-      </c>
-      <c r="F94" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3806,17 +3530,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="F95" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3837,17 +3561,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>52</v>
-      </c>
-      <c r="F96" t="n">
-        <v>81</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3864,11 +3588,9 @@
         <v>3.3</v>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3889,17 +3611,17 @@
           <t>mL/L</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F98" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3920,17 +3642,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F99" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3951,17 +3673,17 @@
           <t>fL</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>12</v>
-      </c>
-      <c r="F100" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3982,17 +3704,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>117</v>
-      </c>
-      <c r="F101" t="n">
-        <v>490</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4013,17 +3735,17 @@
           <t>10^9/L</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>45</v>
-      </c>
-      <c r="F102" t="n">
-        <v>170</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4044,17 +3766,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>20</v>
-      </c>
-      <c r="F103" t="n">
-        <v>60</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4071,11 +3793,9 @@
         <v>120</v>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4096,17 +3816,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F105" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4127,17 +3847,17 @@
           <t>fL</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="F106" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4158,17 +3878,17 @@
           <t>fL</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>60</v>
-      </c>
-      <c r="F107" t="n">
-        <v>76</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>LAB15</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4189,11 +3909,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4214,11 +3932,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4239,17 +3955,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E110" t="n">
-        <v>3900000</v>
-      </c>
-      <c r="F110" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>3900000</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>5200000</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4270,11 +3986,9 @@
           <t>pg</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4295,17 +4009,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v>36</v>
-      </c>
-      <c r="F112" t="n">
-        <v>50</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4326,17 +4040,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>12</v>
-      </c>
-      <c r="F113" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4357,17 +4071,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4388,11 +4102,9 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4413,11 +4125,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4438,11 +4148,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4463,11 +4171,9 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4488,11 +4194,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4513,11 +4217,9 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4538,11 +4240,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4563,17 +4263,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F122" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4590,11 +4290,9 @@
         <v>1.14</v>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4615,11 +4313,9 @@
           <t>fL</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>LAB04</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4640,14 +4336,13 @@
           <t>g%</t>
         </is>
       </c>
-      <c r="F125" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4668,14 +4363,13 @@
           <t>U/l</t>
         </is>
       </c>
-      <c r="F126" t="n">
-        <v>41</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4696,14 +4390,13 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="F127" t="n">
-        <v>2</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4724,14 +4417,13 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>8</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4752,14 +4444,13 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>10</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4780,17 +4471,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F130" t="n">
-        <v>11</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4811,17 +4502,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F131" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4842,17 +4533,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v>150</v>
-      </c>
-      <c r="F132" t="n">
-        <v>200</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4873,11 +4564,9 @@
           <t>ug/dl</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4898,17 +4587,17 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E134" t="n">
-        <v>7</v>
-      </c>
-      <c r="F134" t="n">
-        <v>14</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4929,11 +4618,9 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4950,14 +4637,13 @@
         <v>1025</v>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="n">
-        <v>1025</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4978,17 +4664,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E137" t="n">
-        <v>3900000</v>
-      </c>
-      <c r="F137" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>3900000</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>5200000</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5009,17 +4695,17 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>85</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5040,11 +4726,9 @@
           <t>mg%</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5065,11 +4749,9 @@
           <t>pg</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5090,17 +4772,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>36</v>
-      </c>
-      <c r="F141" t="n">
-        <v>50</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5121,17 +4803,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>12</v>
-      </c>
-      <c r="F142" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5152,17 +4834,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F143" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5183,11 +4865,9 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5208,11 +4888,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5233,11 +4911,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5258,11 +4934,9 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5283,11 +4957,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5308,11 +4980,9 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5333,11 +5003,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5358,17 +5026,17 @@
           <t>mEq/l</t>
         </is>
       </c>
-      <c r="E151" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F151" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5389,11 +5057,9 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5414,17 +5080,17 @@
           <t>g%</t>
         </is>
       </c>
-      <c r="E153" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F153" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5445,17 +5111,17 @@
           <t>mEq/l</t>
         </is>
       </c>
-      <c r="E154" t="n">
-        <v>135</v>
-      </c>
-      <c r="F154" t="n">
-        <v>145</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5476,17 +5142,17 @@
           <t>ng/dl</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F155" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5507,17 +5173,17 @@
           <t>ug/dl</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F156" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5538,14 +5204,13 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>160</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5562,17 +5227,17 @@
         <v>1.7</v>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5593,17 +5258,17 @@
           <t>mg/dl</t>
         </is>
       </c>
-      <c r="E159" t="n">
-        <v>10</v>
-      </c>
-      <c r="F159" t="n">
-        <v>45</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5620,11 +5285,9 @@
         <v>0.8</v>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5645,11 +5308,9 @@
           <t>fL</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>LAB05</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5670,17 +5331,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E162" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F162" t="n">
-        <v>4</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5701,17 +5362,17 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="E163" t="n">
-        <v>10</v>
-      </c>
-      <c r="F163" t="n">
-        <v>60</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5732,17 +5393,17 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="E164" t="n">
-        <v>10</v>
-      </c>
-      <c r="F164" t="n">
-        <v>60</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5763,17 +5424,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E165" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" t="n">
-        <v>50</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5794,11 +5455,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5819,17 +5478,17 @@
           <t>mEq/L</t>
         </is>
       </c>
-      <c r="E167" t="n">
-        <v>105</v>
-      </c>
-      <c r="F167" t="n">
-        <v>129</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5850,17 +5509,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E168" t="n">
-        <v>150</v>
-      </c>
-      <c r="F168" t="n">
-        <v>280</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5881,17 +5540,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E169" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F169" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5912,17 +5571,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E170" t="n">
-        <v>70</v>
-      </c>
-      <c r="F170" t="n">
-        <v>150</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5943,14 +5602,13 @@
           <t>g/L</t>
         </is>
       </c>
-      <c r="E171" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5971,17 +5629,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v>100</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6002,11 +5660,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6027,17 +5683,17 @@
           <t>mill/mm3</t>
         </is>
       </c>
-      <c r="E174" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F174" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6058,14 +5714,13 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>300</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6086,17 +5741,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E176" t="n">
-        <v>3</v>
-      </c>
-      <c r="F176" t="n">
-        <v>6</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6117,17 +5772,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E177" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F177" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6148,11 +5803,9 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6173,17 +5826,17 @@
           <t>pg</t>
         </is>
       </c>
-      <c r="E179" t="n">
-        <v>19</v>
-      </c>
-      <c r="F179" t="n">
-        <v>24</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6204,17 +5857,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E180" t="n">
-        <v>37</v>
-      </c>
-      <c r="F180" t="n">
-        <v>55</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6235,17 +5888,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E181" t="n">
-        <v>12</v>
-      </c>
-      <c r="F181" t="n">
-        <v>19</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6266,17 +5919,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E182" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F182" t="n">
-        <v>17000</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6297,17 +5950,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E183" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F183" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6328,11 +5981,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6353,17 +6004,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E185" t="n">
-        <v>30</v>
-      </c>
-      <c r="F185" t="n">
-        <v>36</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6384,17 +6035,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E186" t="n">
-        <v>150</v>
-      </c>
-      <c r="F186" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6415,11 +6066,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6440,17 +6089,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="n">
-        <v>300</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,11 +6120,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6496,17 +6143,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E190" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F190" t="n">
-        <v>11500</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6527,11 +6174,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6548,17 +6193,17 @@
         <v>6</v>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="n">
-        <v>6</v>
-      </c>
-      <c r="F192" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6579,17 +6224,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v>160000</v>
-      </c>
-      <c r="F193" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6610,17 +6255,17 @@
           <t>mEq/L</t>
         </is>
       </c>
-      <c r="E194" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F194" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6641,11 +6286,9 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6666,17 +6309,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F196" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6693,17 +6336,17 @@
         <v>0.76</v>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F197" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6720,17 +6363,17 @@
         <v>25.64</v>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" t="n">
-        <v>27</v>
-      </c>
-      <c r="F198" t="n">
-        <v>40</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6751,17 +6394,17 @@
           <t>mEq/L</t>
         </is>
       </c>
-      <c r="E199" t="n">
-        <v>140</v>
-      </c>
-      <c r="F199" t="n">
-        <v>155</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6782,17 +6425,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E200" t="n">
-        <v>10</v>
-      </c>
-      <c r="F200" t="n">
-        <v>150</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6809,14 +6452,13 @@
         <v>0.05</v>
       </c>
       <c r="D201" t="inlineStr"/>
-      <c r="F201" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6837,17 +6479,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E202" t="n">
-        <v>20</v>
-      </c>
-      <c r="F202" t="n">
-        <v>50</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6868,17 +6510,17 @@
           <t>fl</t>
         </is>
       </c>
-      <c r="E203" t="n">
-        <v>60</v>
-      </c>
-      <c r="F203" t="n">
-        <v>77</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>LAB02</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6899,17 +6541,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E204" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F204" t="n">
-        <v>4</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6930,17 +6572,17 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="E205" t="n">
-        <v>10</v>
-      </c>
-      <c r="F205" t="n">
-        <v>60</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6961,17 +6603,17 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="E206" t="n">
-        <v>10</v>
-      </c>
-      <c r="F206" t="n">
-        <v>60</v>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6992,17 +6634,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E207" t="n">
-        <v>0</v>
-      </c>
-      <c r="F207" t="n">
-        <v>50</v>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7023,11 +6665,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7048,17 +6688,17 @@
           <t>mEq/L</t>
         </is>
       </c>
-      <c r="E209" t="n">
-        <v>105</v>
-      </c>
-      <c r="F209" t="n">
-        <v>129</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7079,17 +6719,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E210" t="n">
-        <v>150</v>
-      </c>
-      <c r="F210" t="n">
-        <v>280</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7110,11 +6750,9 @@
           <t>ug/l</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7135,17 +6773,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E212" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F212" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7166,17 +6804,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E213" t="n">
-        <v>70</v>
-      </c>
-      <c r="F213" t="n">
-        <v>150</v>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7197,11 +6835,9 @@
           <t>mg%</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7222,14 +6858,13 @@
           <t>g/L</t>
         </is>
       </c>
-      <c r="E215" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7250,17 +6885,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E216" t="n">
-        <v>100</v>
-      </c>
-      <c r="F216" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7281,11 +6916,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7306,17 +6939,17 @@
           <t>mill/mm3</t>
         </is>
       </c>
-      <c r="E218" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F218" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7337,14 +6970,13 @@
           <t>UI/l</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>300</v>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7365,17 +6997,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E220" t="n">
-        <v>3</v>
-      </c>
-      <c r="F220" t="n">
-        <v>6</v>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7396,17 +7028,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E221" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F221" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7427,11 +7059,9 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7452,17 +7082,17 @@
           <t>pg</t>
         </is>
       </c>
-      <c r="E223" t="n">
-        <v>19</v>
-      </c>
-      <c r="F223" t="n">
-        <v>24</v>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7483,17 +7113,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E224" t="n">
-        <v>37</v>
-      </c>
-      <c r="F224" t="n">
-        <v>55</v>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7514,17 +7144,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E225" t="n">
-        <v>12</v>
-      </c>
-      <c r="F225" t="n">
-        <v>19</v>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7545,17 +7175,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E226" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F226" t="n">
-        <v>17000</v>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7576,17 +7206,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E227" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F227" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7607,11 +7237,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7632,17 +7260,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E229" t="n">
-        <v>30</v>
-      </c>
-      <c r="F229" t="n">
-        <v>36</v>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7663,17 +7291,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E230" t="n">
-        <v>150</v>
-      </c>
-      <c r="F230" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7694,11 +7322,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7719,17 +7345,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E232" t="n">
-        <v>0</v>
-      </c>
-      <c r="F232" t="n">
-        <v>300</v>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7750,11 +7376,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7775,17 +7399,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E234" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F234" t="n">
-        <v>11500</v>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7806,11 +7430,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7827,17 +7449,17 @@
         <v>6</v>
       </c>
       <c r="D236" t="inlineStr"/>
-      <c r="E236" t="n">
-        <v>6</v>
-      </c>
-      <c r="F236" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7858,17 +7480,17 @@
           <t>/mm3</t>
         </is>
       </c>
-      <c r="E237" t="n">
-        <v>160000</v>
-      </c>
-      <c r="F237" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7889,17 +7511,17 @@
           <t>mEq/L</t>
         </is>
       </c>
-      <c r="E238" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F238" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7920,11 +7542,9 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7945,17 +7565,17 @@
           <t>g/dl</t>
         </is>
       </c>
-      <c r="E240" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F240" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7972,17 +7592,17 @@
         <v>0.76</v>
       </c>
       <c r="D241" t="inlineStr"/>
-      <c r="E241" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F241" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7999,14 +7619,17 @@
         <v>22.8</v>
       </c>
       <c r="D242" t="inlineStr"/>
-      <c r="F242" t="n">
-        <v>40</v>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8023,17 +7646,17 @@
         <v>25.64</v>
       </c>
       <c r="D243" t="inlineStr"/>
-      <c r="E243" t="n">
-        <v>27</v>
-      </c>
-      <c r="F243" t="n">
-        <v>40</v>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8054,17 +7677,17 @@
           <t>mEq/L</t>
         </is>
       </c>
-      <c r="E244" t="n">
-        <v>140</v>
-      </c>
-      <c r="F244" t="n">
-        <v>155</v>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8085,17 +7708,17 @@
           <t>ng/dl</t>
         </is>
       </c>
-      <c r="E245" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F245" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8116,17 +7739,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E246" t="n">
-        <v>10</v>
-      </c>
-      <c r="F246" t="n">
-        <v>150</v>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8143,14 +7766,13 @@
         <v>0.05</v>
       </c>
       <c r="D247" t="inlineStr"/>
-      <c r="F247" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8171,17 +7793,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E248" t="n">
-        <v>20</v>
-      </c>
-      <c r="F248" t="n">
-        <v>50</v>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8202,17 +7824,17 @@
           <t>fl</t>
         </is>
       </c>
-      <c r="E249" t="n">
-        <v>60</v>
-      </c>
-      <c r="F249" t="n">
-        <v>77</v>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>LAB03</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8233,14 +7855,13 @@
           <t>umol/L</t>
         </is>
       </c>
-      <c r="F250" t="n">
-        <v>25</v>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8261,14 +7882,13 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>1</v>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8289,17 +7909,17 @@
           <t>g/dL</t>
         </is>
       </c>
-      <c r="E252" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F252" t="n">
-        <v>4</v>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8320,17 +7940,17 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="E253" t="n">
-        <v>15</v>
-      </c>
-      <c r="F253" t="n">
-        <v>111</v>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8351,17 +7971,17 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="E254" t="n">
-        <v>500</v>
-      </c>
-      <c r="F254" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8382,17 +8002,17 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="E255" t="n">
-        <v>10</v>
-      </c>
-      <c r="F255" t="n">
-        <v>60</v>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8413,14 +8033,13 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8441,17 +8060,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E257" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F257" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8472,11 +8091,9 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8497,11 +8114,9 @@
           <t>mg2/dL2</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8522,17 +8137,17 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="E260" t="n">
-        <v>10</v>
-      </c>
-      <c r="F260" t="n">
-        <v>200</v>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8549,11 +8164,9 @@
         <v>0.3</v>
       </c>
       <c r="D261" t="inlineStr"/>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8570,11 +8183,9 @@
         <v>75.7</v>
       </c>
       <c r="D262" t="inlineStr"/>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8595,17 +8206,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E263" t="n">
-        <v>108</v>
-      </c>
-      <c r="F263" t="n">
-        <v>290</v>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8626,17 +8237,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E264" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F264" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8657,17 +8268,17 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="E265" t="n">
-        <v>9</v>
-      </c>
-      <c r="F265" t="n">
-        <v>219</v>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8688,17 +8299,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E266" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F266" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8719,14 +8330,13 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="F267" t="n">
-        <v>11</v>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8747,17 +8357,17 @@
           <t>g/dL</t>
         </is>
       </c>
-      <c r="E268" t="n">
-        <v>2</v>
-      </c>
-      <c r="F268" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8778,17 +8388,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E269" t="n">
-        <v>81</v>
-      </c>
-      <c r="F269" t="n">
-        <v>140</v>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8809,17 +8419,17 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="E270" t="n">
-        <v>20</v>
-      </c>
-      <c r="F270" t="n">
-        <v>495</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8840,14 +8450,13 @@
           <t>U/L</t>
         </is>
       </c>
-      <c r="F271" t="n">
-        <v>270</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8868,17 +8477,17 @@
           <t>g/dL</t>
         </is>
       </c>
-      <c r="E272" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F272" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8895,11 +8504,9 @@
         <v>0.48</v>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8920,14 +8527,13 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="F274" t="n">
-        <v>146</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8948,17 +8554,17 @@
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="E275" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F275" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>LAB14</t>
-        </is>
-      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>55.9</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8971,15 +8577,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
@@ -9029,72 +8635,96 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Métricas CGM caninas (TIR/TAR/CV)</t>
+          <t>Métricas CGM en perros diabéticos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PMC12175195 (2025): FreeStyle Libre-derived metrics in diabetic dogs</t>
+          <t>FreeStyle Libre metrics in diabetic dogs, PMC12175195 (TIR/TAR/media/CV)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eAG = 0,59·F − 9,6</t>
+          <t>eAG = 0,59x F - 9,6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kang DS et al 2015, PMC4397269</t>
+          <t>Kang DS 2015, Canine fructosamine, PMC4397269</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cut-offs caninos fructosamina</t>
+          <t>Cut-offs caninos de fructosamina</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PMC8880912 (A1CARE): &lt;360 BUENO / 360-442 REGULAR / &gt;=443 MALO</t>
+          <t>GOOD &lt;360 / FAIR 360-442 / POOR &gt;=443, PMC8880912</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fructosamina refleja hipos recientes</t>
+          <t>Fructosamina e hipoglucemias</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kuzi S et al 2023, Vet Record, DOI 10.1002/vetr.2236</t>
+          <t>Kuzi S 2023, Vet Record, DOI 10.1002/vetr.2236</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CV% &lt;36% umbral de riesgo hipo</t>
+          <t>CV &lt;36% umbral riesgo de hipo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Castañeda et al 2023, Diabetes Obes Metab, DOI 10.1111/dom.15139; Mo et al 2020, PMC8169344</t>
+          <t>Castañeda 2023 DOI 10.1111/dom.15139; Mo 2020 PMC8169344</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Variabilidad dia-a-dia insulina</t>
+          <t>Variabilidad día-a-día de insulina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JVIM 2021, DOI 10.1111/jvim.16006</t>
+          <t>JVIM 2021, day-to-day CV entre formulaciones, DOI 10.1111/jvim.16006</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Antibióticos en diarrea crónica canina</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Metronidazol/tilosina como elección; amoxicilina no primera línea, PMC7079140</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cobalamina (B12) en enteropatía crónica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Déficit = mala prognosis; suplementación mejora clínica, PMC11898182</t>
         </is>
       </c>
     </row>
@@ -9109,15 +8739,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Abreviatura</t>
         </is>
@@ -9191,120 +8821,108 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GLU</t>
+          <t>GLU / F</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Glucosa (lecturas de planillas, mg/dL)</t>
+          <t>Glucosa (planillas) / Fructosamina (µmol/L)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>eAG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fructosamina (µmol/L)</t>
+          <t>Glucosa promedio estimada (estimated average glucose)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eAG</t>
+          <t>CGM / BG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Glucosa promedio estimada (estimated average glucose)</t>
+          <t>Monitorización continua de glucosa / Glucosa sanguínea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CGM / BG</t>
+          <t>UCCR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monitorización continua de glucosa / Glucosa sanguínea</t>
+          <t>Cociente cortisol-creatinina urinaria (control del Cushing)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UCCR</t>
+          <t>UPC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cociente cortisol-creatinina urinaria (control del Cushing)</t>
+          <t>Cociente proteína-creatinina urinaria (proteinuria)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UPC</t>
+          <t>LPCE (cPLI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cociente proteína-creatinina urinaria (proteinuria)</t>
+          <t>Lipasa pancreática específica canina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPCE / cPLI</t>
+          <t>Hto / Hb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lipasa pancreática específica canina</t>
+          <t>Hematocrito / Hemoglobina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hto / Hb</t>
+          <t>T4 libre / TSH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hematocrito / Hemoglobina</t>
+          <t>Tiroxina libre / Hormona estimulante de la tiroides</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T4 libre / TSH</t>
+          <t>ALT / FAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tiroxina libre / Hormona estimulante de la tiroides</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ALT (GPT) / FAL / GGT</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Enzimas hepáticas: alanina-aminotransferasa / fosfatasa alcalina / gamma-glutamil transferasa</t>
+          <t>Enzimas hepáticas: alanina-aminotransferasa / fosfatasa alcalina</t>
         </is>
       </c>
     </row>
@@ -9322,8 +8940,8 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9332,7 +8950,7 @@
           <t>Aviso</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Estas hojas de análisis fueron generadas por inteligencia artificial a partir de las bases de datos domiciliarias y la bibliografía citada. No constituyen diagnóstico ni sustituyen el criterio veterinario. Los valores domiciliarios son autorreportados.</t>
         </is>
